--- a/business-libraries/test-data/class_system/keyword_route.xlsx
+++ b/business-libraries/test-data/class_system/keyword_route.xlsx
@@ -448,16 +448,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KW_C_01</v>
+        <v>CS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>班级管理</v>
+        <v>班级乱,管不住,纪律差</v>
       </c>
       <c r="C2" t="str">
-        <v>班级管理相关；工作压力大；感觉疲惫</v>
+        <v>课堂混乱,说话没人听</v>
       </c>
       <c r="D2" t="str">
-        <v>开玩笑的表达；反讽</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>class_system</v>
@@ -466,42 +466,42 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>exact</v>
+        <v>fuzzy</v>
       </c>
       <c r="H2" t="str">
-        <v>red</v>
+        <v>orange</v>
       </c>
       <c r="I2" t="str">
-        <v>班级管理</v>
+        <v>秩序问题</v>
       </c>
       <c r="J2" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="K2" t="str">
-        <v>C_RX_001</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="L2" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>1.0</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师在对话中表达班级管理相关信号，触发班级系统建设模块评估和工具推荐</v>
+        <v>教师表达班级秩序失控</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KW_C_02</v>
+        <v>CS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>课堂纪律</v>
+        <v>班干部,岗位,分工</v>
       </c>
       <c r="C3" t="str">
-        <v>课堂纪律相关；课堂纪律表现</v>
+        <v>没人干活,都要我自己来</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -510,22 +510,22 @@
         <v>class_system</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H3" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>课堂纪律</v>
+        <v>组织问题</v>
       </c>
       <c r="J3" t="str">
-        <v>C_FIVE_Q</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="K3" t="str">
-        <v>C_RX_002</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,18 +537,18 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达课堂纪律相关困扰，推荐对应自我照顾工具</v>
+        <v>教师表达班级事务过度集中</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KW_C_03</v>
+        <v>CS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>学生打架</v>
+        <v>打架,吵架,同学矛盾</v>
       </c>
       <c r="C4" t="str">
-        <v>学生打架相关；情绪不良</v>
+        <v>闹翻了,不理人,起冲突</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -557,45 +557,45 @@
         <v>class_system</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I4" t="str">
-        <v>学生打架</v>
+        <v>关系冲突</v>
       </c>
       <c r="J4" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="K4" t="str">
-        <v>C_RX_003</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="L4" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达学生打架相关信号，推荐同伴支持或自评</v>
+        <v>班级内出现同伴冲突</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KW_C_04</v>
+        <v>CS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>班级混乱</v>
+        <v>被孤立,没朋友,不合群</v>
       </c>
       <c r="C5" t="str">
-        <v>班级混乱相关；无精打采</v>
+        <v>没人跟他玩,排挤</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -604,34 +604,34 @@
         <v>class_system</v>
       </c>
       <c r="F5" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I5" t="str">
-        <v>班级混乱</v>
+        <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>C_QUICK</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="K5" t="str">
-        <v>C_RX_004</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>教师表达班级混乱相关信号，推荐认知类工具</v>
+        <v>出现学生被孤立的信号</v>
       </c>
     </row>
   </sheetData>

--- a/business-libraries/test-data/class_system/keyword_route.xlsx
+++ b/business-libraries/test-data/class_system/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>CS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>班级乱,管不住,纪律差</v>
+        <v>班级乱;管不住;纪律差</v>
       </c>
       <c r="C2" t="str">
-        <v>课堂混乱,说话没人听</v>
+        <v>课堂混乱;说话没人听</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>秩序问题</v>
       </c>
       <c r="J2" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>CS_RX_004</v>
+        <v>CS_RX_04</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>CS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>班干部,岗位,分工</v>
+        <v>班干部;岗位;分工</v>
       </c>
       <c r="C3" t="str">
-        <v>没人干活,都要我自己来</v>
+        <v>没人干活;都要我自己来</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>组织问题</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_FIVE_SYS</v>
+        <v>CS_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>CS_RX_002</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>CS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>打架,吵架,同学矛盾</v>
+        <v>打架;吵架;同学矛盾</v>
       </c>
       <c r="C4" t="str">
-        <v>闹翻了,不理人,起冲突</v>
+        <v>闹翻了;不理人;起冲突</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>关系冲突</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="K4" t="str">
-        <v>CS_RX_005</v>
+        <v>CS_RX_05</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>CS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被孤立,没朋友,不合群</v>
+        <v>被孤立;没朋友;不合群</v>
       </c>
       <c r="C5" t="str">
-        <v>没人跟他玩,排挤</v>
+        <v>没人跟他玩;排挤</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,10 +616,10 @@
         <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>CS_ENERGY</v>
+        <v>CS_S2</v>
       </c>
       <c r="K5" t="str">
-        <v>CS_RX_006</v>
+        <v>CS_RX_06</v>
       </c>
       <c r="L5" t="str">
         <v/>

--- a/business-libraries/test-data/class_system/keyword_route.xlsx
+++ b/business-libraries/test-data/class_system/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>CS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>班级乱;管不住;纪律差</v>
+        <v>班级乱,管不住,纪律差</v>
       </c>
       <c r="C2" t="str">
-        <v>课堂混乱;说话没人听</v>
+        <v>课堂混乱,说话没人听</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>秩序问题</v>
       </c>
       <c r="J2" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="K2" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_004</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>CS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>班干部;岗位;分工</v>
+        <v>班干部,岗位,分工</v>
       </c>
       <c r="C3" t="str">
-        <v>没人干活;都要我自己来</v>
+        <v>没人干活,都要我自己来</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>组织问题</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_S1</v>
+        <v>CS_FIVE_SYS</v>
       </c>
       <c r="K3" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_002</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>CS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>打架;吵架;同学矛盾</v>
+        <v>打架,吵架,同学矛盾</v>
       </c>
       <c r="C4" t="str">
-        <v>闹翻了;不理人;起冲突</v>
+        <v>闹翻了,不理人,起冲突</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>关系冲突</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="K4" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_005</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>CS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被孤立;没朋友;不合群</v>
+        <v>被孤立,没朋友,不合群</v>
       </c>
       <c r="C5" t="str">
-        <v>没人跟他玩;排挤</v>
+        <v>没人跟他玩,排挤</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,10 +616,10 @@
         <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>CS_S2</v>
+        <v>CS_ENERGY</v>
       </c>
       <c r="K5" t="str">
-        <v>CS_RX_06</v>
+        <v>CS_RX_006</v>
       </c>
       <c r="L5" t="str">
         <v/>

--- a/business-libraries/test-data/class_system/keyword_route.xlsx
+++ b/business-libraries/test-data/class_system/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,10 +451,10 @@
         <v>CS_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>班级乱;管不住;纪律差</v>
+        <v>五系统;班级系统</v>
       </c>
       <c r="C2" t="str">
-        <v>课堂混乱;说话没人听</v>
+        <v>定位短板;班级体检</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -469,16 +469,16 @@
         <v>fuzzy</v>
       </c>
       <c r="H2" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I2" t="str">
-        <v>秩序问题</v>
+        <v>诊断框架类</v>
       </c>
       <c r="J2" t="str">
         <v>CS_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>CS_RX_04</v>
+        <v>CS_RX_01</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -490,7 +490,7 @@
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师表达班级秩序失控</v>
+        <v>五系统诊断模型：定位短板属于哪类系统</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>CS_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>班干部;岗位;分工</v>
+        <v>能量场;班级氛围</v>
       </c>
       <c r="C3" t="str">
-        <v>没人干活;都要我自己来</v>
+        <v>生命体征;集体势能</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -519,13 +519,13 @@
         <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>组织问题</v>
+        <v>诊断框架类</v>
       </c>
       <c r="J3" t="str">
-        <v>CS_S1</v>
+        <v>CS_S2</v>
       </c>
       <c r="K3" t="str">
-        <v>CS_RX_02</v>
+        <v>CS_RX_09</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达班级事务过度集中</v>
+        <v>班级能量场：无形心理氛围与集体势能</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>CS_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>打架;吵架;同学矛盾</v>
+        <v>堰塞湖;问题积累</v>
       </c>
       <c r="C4" t="str">
-        <v>闹翻了;不理人;起冲突</v>
+        <v>突然爆发;集体辞职;凝聚力骤降</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -566,13 +566,13 @@
         <v>orange</v>
       </c>
       <c r="I4" t="str">
-        <v>关系冲突</v>
+        <v>诊断框架类</v>
       </c>
       <c r="J4" t="str">
-        <v>CS_S2</v>
+        <v>CS_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>CS_RX_05</v>
+        <v>CS_RX_02</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -584,7 +584,7 @@
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>班级内出现同伴冲突</v>
+        <v>堰塞湖模型：问题积累到爆发，需在低水位时疏通</v>
       </c>
     </row>
     <row r="5">
@@ -592,10 +592,10 @@
         <v>CS_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被孤立;没朋友;不合群</v>
+        <v>能力意愿;个案诊断</v>
       </c>
       <c r="C5" t="str">
-        <v>没人跟他玩;排挤</v>
+        <v>成功型;挫折型;对抗型;放弃型</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -610,33 +610,1490 @@
         <v>fuzzy</v>
       </c>
       <c r="H5" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I5" t="str">
+        <v>诊断框架类</v>
+      </c>
+      <c r="J5" t="str">
+        <v>CS_S9</v>
+      </c>
+      <c r="K5" t="str">
+        <v>CS_RX_03</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N5" t="str">
+        <v>always</v>
+      </c>
+      <c r="O5" t="str">
+        <v>能力×意愿矩阵：个体行为问题归因</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CS_KW_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>五星评价;五星班级</v>
+      </c>
+      <c r="C6" t="str">
+        <v>德育常规;学风管理;家校共育</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F6" t="str">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H6" t="str">
+        <v>green</v>
+      </c>
+      <c r="I6" t="str">
+        <v>评价与制度类</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>CS_RX_16</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N6" t="str">
+        <v>always</v>
+      </c>
+      <c r="O6" t="str">
+        <v>五星评价：三维度1-5星，月度评定</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CS_KW_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>三通;家校群</v>
+      </c>
+      <c r="C7" t="str">
+        <v>通情;通理;通力</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F7" t="str">
+        <v>6</v>
+      </c>
+      <c r="G7" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H7" t="str">
+        <v>green</v>
+      </c>
+      <c r="I7" t="str">
+        <v>评价与制度类</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N7" t="str">
+        <v>always</v>
+      </c>
+      <c r="O7" t="str">
+        <v>三通工程：家校协同三项机制，关键是持续做</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CS_KW_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>心理风险;A-E;安全危机</v>
+      </c>
+      <c r="C8" t="str">
+        <v>高风险;自伤;上报</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F8" t="str">
+        <v>7</v>
+      </c>
+      <c r="G8" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H8" t="str">
+        <v>red</v>
+      </c>
+      <c r="I8" t="str">
+        <v>评价与制度类</v>
+      </c>
+      <c r="J8" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K8" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N8" t="str">
+        <v>always</v>
+      </c>
+      <c r="O8" t="str">
+        <v>心理风险A-E五级，A/B级须24-48h上报</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CS_KW_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SDQ;优势困难问卷</v>
+      </c>
+      <c r="C9" t="str">
+        <v>情绪症状;隐形焦虑</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F9" t="str">
+        <v>8</v>
+      </c>
+      <c r="G9" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H9" t="str">
         <v>orange</v>
       </c>
-      <c r="I5" t="str">
-        <v>同伴排斥</v>
-      </c>
-      <c r="J5" t="str">
+      <c r="I9" t="str">
+        <v>评价与制度类</v>
+      </c>
+      <c r="J9" t="str">
+        <v>CS_S10</v>
+      </c>
+      <c r="K9" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N9" t="str">
+        <v>always</v>
+      </c>
+      <c r="O9" t="str">
+        <v>SDQ外部量表，筛查非诊断，严禁贴标签</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CS_KW_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>VIA;品格优势;优势卡</v>
+      </c>
+      <c r="C10" t="str">
+        <v>创造力;勇敢;仁爱</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F10" t="str">
+        <v>9</v>
+      </c>
+      <c r="G10" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H10" t="str">
+        <v>green</v>
+      </c>
+      <c r="I10" t="str">
+        <v>评价与制度类</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>CS_RX_23</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N10" t="str">
+        <v>always</v>
+      </c>
+      <c r="O10" t="str">
+        <v>VIA品格优势：SDQ查困难，VIA查优势</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CS_KW_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>依恋;回避型;焦虑型;混乱型</v>
+      </c>
+      <c r="C11" t="str">
+        <v>安全基地;插嘴;不服管</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+      <c r="G11" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H11" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I11" t="str">
+        <v>关系与依恋类</v>
+      </c>
+      <c r="J11" t="str">
+        <v>CS_S8</v>
+      </c>
+      <c r="K11" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N11" t="str">
+        <v>always</v>
+      </c>
+      <c r="O11" t="str">
+        <v>依恋关系四型：问题行为多与依恋根源有关</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CS_KW_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>安全基地</v>
+      </c>
+      <c r="C12" t="str">
+        <v>补偿性安全基地;在这里是安全的</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F12" t="str">
+        <v>11</v>
+      </c>
+      <c r="G12" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H12" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I12" t="str">
+        <v>关系与依恋类</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>CS_RX_08</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N12" t="str">
+        <v>always</v>
+      </c>
+      <c r="O12" t="str">
+        <v>安全基地：安全感充足的孩子更敢探索</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CS_KW_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>73855;沟通密码</v>
+      </c>
+      <c r="C13" t="str">
+        <v>7%文字;38%语调;55%肢体</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F13" t="str">
+        <v>12</v>
+      </c>
+      <c r="G13" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H13" t="str">
+        <v>green</v>
+      </c>
+      <c r="I13" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>CS_RX_29</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N13" t="str">
+        <v>always</v>
+      </c>
+      <c r="O13" t="str">
+        <v>73855法则：70%积极+30%待改进的结构化表达</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CS_KW_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>意义换框</v>
+      </c>
+      <c r="C14" t="str">
+        <v>成长课题;重构</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F14" t="str">
+        <v>13</v>
+      </c>
+      <c r="G14" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H14" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I14" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N14" t="str">
+        <v>always</v>
+      </c>
+      <c r="O14" t="str">
+        <v>意义换框法：从负面事件挖出正面意义</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CS_KW_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>EQ;处理情绪</v>
+      </c>
+      <c r="C15" t="str">
+        <v>停听标析选;情绪沟通</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F15" t="str">
+        <v>14</v>
+      </c>
+      <c r="G15" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H15" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I15" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J15" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K15" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N15" t="str">
+        <v>always</v>
+      </c>
+      <c r="O15" t="str">
+        <v>EQ型处理情绪：停-听-标-析-选五步</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CS_KW_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>六步脱困;我做不到</v>
+      </c>
+      <c r="C16" t="str">
+        <v>还没做到;限制性信念</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+      <c r="G16" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H16" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I16" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N16" t="str">
+        <v>always</v>
+      </c>
+      <c r="O16" t="str">
+        <v>六步脱困法：把『我做不到』变成『我还没做到』</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CS_KW_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>经典八问</v>
+      </c>
+      <c r="C17" t="str">
+        <v>结构化提问;问题解决</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F17" t="str">
+        <v>16</v>
+      </c>
+      <c r="G17" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H17" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I17" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N17" t="str">
+        <v>always</v>
+      </c>
+      <c r="O17" t="str">
+        <v>经典八问：上手最快、适用范围最广的结构化提问</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CS_KW_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>先跟后带</v>
+      </c>
+      <c r="C18" t="str">
+        <v>对抗;共情跟随;上堆</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F18" t="str">
+        <v>17</v>
+      </c>
+      <c r="G18" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H18" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I18" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N18" t="str">
+        <v>always</v>
+      </c>
+      <c r="O18" t="str">
+        <v>先跟后带：处理沟通模式与对抗</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CS_KW_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>内感官</v>
+      </c>
+      <c r="C19" t="str">
+        <v>视觉型;听觉型;感觉型</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F19" t="str">
+        <v>18</v>
+      </c>
+      <c r="G19" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H19" t="str">
+        <v>green</v>
+      </c>
+      <c r="I19" t="str">
+        <v>密码本技术类</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>CS_RX_07</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N19" t="str">
+        <v>always</v>
+      </c>
+      <c r="O19" t="str">
+        <v>内感官：按信息接收偏好提升沟通效率</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CS_KW_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>正念;注意力训练</v>
+      </c>
+      <c r="C20" t="str">
+        <v>葡萄干练习;大脑充电器;静不下来</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F20" t="str">
+        <v>19</v>
+      </c>
+      <c r="G20" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H20" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I20" t="str">
+        <v>积极心理类</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>CS_RX_22</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N20" t="str">
+        <v>always</v>
+      </c>
+      <c r="O20" t="str">
+        <v>正念教育：对『静不下来/注意力散/情绪爆发』有效</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CS_KW_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Kagan;合作学习</v>
+      </c>
+      <c r="C21" t="str">
+        <v>时钟伙伴;小组讨论;搭便车</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
+      <c r="G21" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H21" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I21" t="str">
+        <v>积极心理类</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>CS_RX_13</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N21" t="str">
+        <v>always</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Kagan合作学习：解决少数人发言/搭便车/闲聊</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CS_KW_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>成长型思维</v>
+      </c>
+      <c r="C22" t="str">
+        <v>我不行;还没找到方法;错误分析档案</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F22" t="str">
+        <v>21</v>
+      </c>
+      <c r="G22" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H22" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I22" t="str">
+        <v>积极心理类</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>CS_RX_19</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N22" t="str">
+        <v>always</v>
+      </c>
+      <c r="O22" t="str">
+        <v>成长型思维：把『我不行』重框为『还没找到方法』</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CS_KW_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>PERMA</v>
+      </c>
+      <c r="C23" t="str">
+        <v>积极情绪;投入;关系;意义;成就</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F23" t="str">
+        <v>22</v>
+      </c>
+      <c r="G23" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H23" t="str">
+        <v>green</v>
+      </c>
+      <c r="I23" t="str">
+        <v>积极心理类</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>CS_RX_24</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N23" t="str">
+        <v>always</v>
+      </c>
+      <c r="O23" t="str">
+        <v>PERMA幸福公式：每月选一维度设计班级活动</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CS_KW_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>区块长</v>
+      </c>
+      <c r="C24" t="str">
+        <v>人人有事做;事事有人管;责任区划</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F24" t="str">
+        <v>23</v>
+      </c>
+      <c r="G24" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H24" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I24" t="str">
+        <v>组织与规范类</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N24" t="str">
+        <v>always</v>
+      </c>
+      <c r="O24" t="str">
+        <v>区块长：责任区划由学生认领，避免只靠班委</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CS_KW_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>大管家;小管家</v>
+      </c>
+      <c r="C25" t="str">
+        <v>班干部;班级小管家</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F25" t="str">
+        <v>24</v>
+      </c>
+      <c r="G25" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H25" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I25" t="str">
+        <v>组织与规范类</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>CS_RX_10</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N25" t="str">
+        <v>always</v>
+      </c>
+      <c r="O25" t="str">
+        <v>大管家+小管家：班级服务者角色重构</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CS_KW_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>班委;竞选;班干部</v>
+      </c>
+      <c r="C26" t="str">
+        <v>岗位答辩;试用考核;没人干活</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F26" t="str">
+        <v>25</v>
+      </c>
+      <c r="G26" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H26" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I26" t="str">
+        <v>组织与规范类</v>
+      </c>
+      <c r="J26" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>CS_RX_04</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N26" t="str">
+        <v>always</v>
+      </c>
+      <c r="O26" t="str">
+        <v>班委选拔六步法：组建服务型班委</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CS_KW_26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>公约;班规;班级规则</v>
+      </c>
+      <c r="C27" t="str">
+        <v>签字上墙;规则没人听</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F27" t="str">
+        <v>26</v>
+      </c>
+      <c r="G27" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H27" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I27" t="str">
+        <v>组织与规范类</v>
+      </c>
+      <c r="J27" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>CS_RX_05</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N27" t="str">
+        <v>always</v>
+      </c>
+      <c r="O27" t="str">
+        <v>班级公约六步法：民主制定软规则</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CS_KW_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>修复性对话;冲突修复</v>
+      </c>
+      <c r="C28" t="str">
+        <v>打闹;告状;修复约定</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F28" t="str">
+        <v>27</v>
+      </c>
+      <c r="G28" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H28" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I28" t="str">
+        <v>组织与规范类</v>
+      </c>
+      <c r="J28" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K28" t="str">
+        <v>CS_RX_06</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N28" t="str">
+        <v>always</v>
+      </c>
+      <c r="O28" t="str">
+        <v>修复性对话：聚焦修复而非追责</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CS_KW_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>危机;危机响应</v>
+      </c>
+      <c r="C29" t="str">
+        <v>自伤;欺凌;漏报;迟报</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F29" t="str">
+        <v>28</v>
+      </c>
+      <c r="G29" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H29" t="str">
+        <v>red</v>
+      </c>
+      <c r="I29" t="str">
+        <v>危机与筛查类</v>
+      </c>
+      <c r="J29" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K29" t="str">
+        <v>CS_RX_25</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N29" t="str">
+        <v>always</v>
+      </c>
+      <c r="O29" t="str">
+        <v>危机响应A-E分级：以制度原文A-E五级为准</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>CS_KW_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>情绪崩溃;情绪急救</v>
+      </c>
+      <c r="C30" t="str">
+        <v>大哭;失控;现场处置</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F30" t="str">
+        <v>29</v>
+      </c>
+      <c r="G30" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H30" t="str">
+        <v>red</v>
+      </c>
+      <c r="I30" t="str">
+        <v>危机与筛查类</v>
+      </c>
+      <c r="J30" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K30" t="str">
+        <v>CS_RX_28</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N30" t="str">
+        <v>always</v>
+      </c>
+      <c r="O30" t="str">
+        <v>情绪急救三步法：停-听-析选</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>CS_KW_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>绘画;房树人;雨中人;树木画</v>
+      </c>
+      <c r="C31" t="str">
+        <v>红旗清单;转介</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F31" t="str">
+        <v>30</v>
+      </c>
+      <c r="G31" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H31" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I31" t="str">
+        <v>危机与筛查类</v>
+      </c>
+      <c r="J31" t="str">
+        <v>CS_S7</v>
+      </c>
+      <c r="K31" t="str">
+        <v>CS_RX_27</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N31" t="str">
+        <v>always</v>
+      </c>
+      <c r="O31" t="str">
+        <v>绘画投射筛查：筛查非诊断，红橙级转介</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CS_KW_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>班级乱;纪律差;管不住</v>
+      </c>
+      <c r="C32" t="str">
+        <v>课堂混乱;说话没人听;违规反复</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F32" t="str">
+        <v>31</v>
+      </c>
+      <c r="G32" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H32" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I32" t="str">
+        <v>场景路由</v>
+      </c>
+      <c r="J32" t="str">
+        <v>CS_S1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>CS_RX_14</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N32" t="str">
+        <v>always</v>
+      </c>
+      <c r="O32" t="str">
+        <v>班级秩序失控：规则认同与督导问题</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CS_KW_32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>打架;吵架;同学矛盾</v>
+      </c>
+      <c r="C33" t="str">
+        <v>闹翻了;不理人;起冲突</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F33" t="str">
+        <v>32</v>
+      </c>
+      <c r="G33" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H33" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I33" t="str">
+        <v>场景路由</v>
+      </c>
+      <c r="J33" t="str">
         <v>CS_S2</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K33" t="str">
         <v>CS_RX_06</v>
       </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="N5" t="str">
-        <v>always</v>
-      </c>
-      <c r="O5" t="str">
-        <v>出现学生被孤立的信号</v>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N33" t="str">
+        <v>always</v>
+      </c>
+      <c r="O33" t="str">
+        <v>同伴冲突：需要修复性对话与缓冲层</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CS_KW_33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>被孤立;没朋友;不合群</v>
+      </c>
+      <c r="C34" t="str">
+        <v>没人跟他玩;排挤;隐形人</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F34" t="str">
+        <v>33</v>
+      </c>
+      <c r="G34" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H34" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I34" t="str">
+        <v>场景路由</v>
+      </c>
+      <c r="J34" t="str">
+        <v>CS_S3</v>
+      </c>
+      <c r="K34" t="str">
+        <v>CS_RX_09</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N34" t="str">
+        <v>always</v>
+      </c>
+      <c r="O34" t="str">
+        <v>同伴排斥与孤立：归属感连接通道缺失</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>CS_KW_34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>成绩下滑;知识欠账;跟不上</v>
+      </c>
+      <c r="C35" t="str">
+        <v>断崖式下跌;听不懂</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F35" t="str">
+        <v>34</v>
+      </c>
+      <c r="G35" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H35" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I35" t="str">
+        <v>场景路由</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>CS_RX_02</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N35" t="str">
+        <v>always</v>
+      </c>
+      <c r="O35" t="str">
+        <v>学业欠账堆积：需溯源补漏、降难度回填</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>CS_KW_35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>情绪失控;发脾气;哭闹</v>
+      </c>
+      <c r="C36" t="str">
+        <v>情绪角;冷静角</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="F36" t="str">
+        <v>35</v>
+      </c>
+      <c r="G36" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H36" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I36" t="str">
+        <v>场景路由</v>
+      </c>
+      <c r="J36" t="str">
+        <v>CS_S6</v>
+      </c>
+      <c r="K36" t="str">
+        <v>CS_RX_21</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N36" t="str">
+        <v>always</v>
+      </c>
+      <c r="O36" t="str">
+        <v>情绪失控：先给安全空间再接住情绪</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O36"/>
   </ignoredErrors>
 </worksheet>
 </file>